--- a/Section V Results and Discussion/Training-1/ReviewersdataRankingv7.xlsx
+++ b/Section V Results and Discussion/Training-1/ReviewersdataRankingv7.xlsx
@@ -721,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -732,6 +732,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1134,11 +1135,11 @@
       <c r="E2" s="4">
         <v>83.4434</v>
       </c>
-      <c r="F2" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G2" s="4">
-        <v>15.3118</v>
+      <c r="F2" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G2" s="5">
+        <v>55.5315827</v>
       </c>
       <c r="H2" s="4">
         <v>0.992635145087642</v>
@@ -1166,11 +1167,11 @@
       <c r="E3" s="4">
         <v>120.7342</v>
       </c>
-      <c r="F3" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G3" s="4">
-        <v>22.1547</v>
+      <c r="F3" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G3" s="5">
+        <v>80.3486101</v>
       </c>
       <c r="H3" s="4">
         <v>0.98994</v>
@@ -1198,11 +1199,11 @@
       <c r="E4" s="4">
         <v>116.8817</v>
       </c>
-      <c r="F4" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G4" s="4">
-        <v>21.4477</v>
+      <c r="F4" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G4" s="5">
+        <v>77.78477135</v>
       </c>
       <c r="H4" s="4">
         <v>0.991141131662563</v>
@@ -1230,11 +1231,11 @@
       <c r="E5" s="4">
         <v>45.5027</v>
       </c>
-      <c r="F5" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G5" s="4">
-        <v>8.3497</v>
+      <c r="F5" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G5" s="5">
+        <v>30.28204685</v>
       </c>
       <c r="H5" s="4">
         <v>0.96</v>
@@ -1262,11 +1263,11 @@
       <c r="E6" s="4">
         <v>211.9776</v>
       </c>
-      <c r="F6" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G6" s="4">
-        <v>38.8978</v>
+      <c r="F6" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G6" s="5">
+        <v>141.0710928</v>
       </c>
       <c r="H6" s="4">
         <v>0.997306567346338</v>
@@ -1294,11 +1295,11 @@
       <c r="E7" s="4">
         <v>59.6333</v>
       </c>
-      <c r="F7" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G7" s="4">
-        <v>10.9427</v>
+      <c r="F7" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G7" s="5">
+        <v>39.68596115</v>
       </c>
       <c r="H7" s="4">
         <v>0.979378406245397</v>
@@ -1326,11 +1327,11 @@
       <c r="E8" s="4">
         <v>82.3644</v>
       </c>
-      <c r="F8" s="4">
-        <v>0.18355</v>
-      </c>
-      <c r="G8" s="4">
-        <v>15.1138</v>
+      <c r="F8" s="5">
+        <v>0.6655</v>
+      </c>
+      <c r="G8" s="5">
+        <v>54.8135082</v>
       </c>
       <c r="H8" s="4">
         <v>0.99522336552827</v>
